--- a/MsPFM/AIC8822/MsTables/WF_MEASURE_TABLE_20240628_V3.xlsx
+++ b/MsPFM/AIC8822/MsTables/WF_MEASURE_TABLE_20240628_V3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26670" windowHeight="14040"/>
+    <workbookView windowWidth="28800" windowHeight="14340"/>
   </bookViews>
   <sheets>
     <sheet name="PMS" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="29">
   <si>
     <t>TEST_ENABLE</t>
   </si>
@@ -67,7 +67,7 @@
     <t>10 24 1</t>
   </si>
   <si>
-    <t>NA</t>
+    <t>r 403422c8</t>
   </si>
   <si>
     <t>N</t>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
@@ -1191,7 +1191,7 @@
     </row>
     <row r="4" ht="11" customHeight="1" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -1261,7 +1261,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>22</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>22</v>
@@ -1383,9 +1383,7 @@
       <c r="F9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
         <v>11</v>
       </c>
@@ -1418,9 +1416,7 @@
       <c r="F10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
         <v>11</v>
       </c>
@@ -1453,9 +1449,7 @@
       <c r="F11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
         <v>11</v>
       </c>
@@ -1488,9 +1482,7 @@
       <c r="F12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="G12" s="2"/>
       <c r="H12" s="2" t="s">
         <v>11</v>
       </c>
@@ -1523,9 +1515,7 @@
       <c r="F13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="G13" s="2"/>
       <c r="H13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1558,9 +1548,7 @@
       <c r="F14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="G14" s="2"/>
       <c r="H14" s="2" t="s">
         <v>11</v>
       </c>
@@ -1593,9 +1581,7 @@
       <c r="F15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1628,9 +1614,7 @@
       <c r="F16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
         <v>11</v>
       </c>
@@ -1663,9 +1647,7 @@
       <c r="F17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
         <v>11</v>
       </c>
@@ -1698,9 +1680,7 @@
       <c r="F18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
         <v>11</v>
       </c>
@@ -1733,9 +1713,7 @@
       <c r="F19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
         <v>11</v>
       </c>
@@ -1786,7 +1764,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>28</v>
@@ -1821,7 +1799,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>28</v>
